--- a/data/trans_orig/IP26C_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP26C_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2007 (tasa de respuesta: 99,43%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2007 (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>18314</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>11234</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12315</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25508</t>
+          <t>24955</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72461</t>
+          <t>72553</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83214</t>
+          <t>83333</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74992</t>
+          <t>74907</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82994</t>
+          <t>83075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151500</t>
+          <t>152053</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>164693</t>
+          <t>164874</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,14%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37602</t>
+          <t>38472</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58750</t>
+          <t>58790</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36944</t>
+          <t>35975</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57337</t>
+          <t>57310</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80472</t>
+          <t>77478</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108610</t>
+          <t>108334</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356715</t>
+          <t>356675</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>377863</t>
+          <t>376993</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>415546</t>
+          <t>415573</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>435939</t>
+          <t>436908</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>779738</t>
+          <t>780014</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>807876</t>
+          <t>810870</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>12978</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26299</t>
+          <t>26452</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10508</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23818</t>
+          <t>22388</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26713</t>
+          <t>26479</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44299</t>
+          <t>44834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>146398</t>
+          <t>146245</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>159891</t>
+          <t>159719</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132987</t>
+          <t>134417</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>146503</t>
+          <t>146297</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>285203</t>
+          <t>284668</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>302789</t>
+          <t>303023</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65248</t>
+          <t>65682</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92607</t>
+          <t>92845</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55686</t>
+          <t>55832</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81987</t>
+          <t>80371</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127529</t>
+          <t>129479</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165580</t>
+          <t>165012</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>586422</t>
+          <t>586184</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>613781</t>
+          <t>613347</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>633841</t>
+          <t>635457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>660142</t>
+          <t>659996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1229278</t>
+          <t>1229846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1267329</t>
+          <t>1265379</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,72%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2012 (tasa de respuesta: 98,9%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2012 (tasa de respuesta: 98,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17054</t>
+          <t>16888</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21000</t>
+          <t>20988</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>19186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34063</t>
+          <t>34129</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75315</t>
+          <t>75481</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85881</t>
+          <t>85999</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65192</t>
+          <t>65204</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76776</t>
+          <t>76679</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144498</t>
+          <t>144432</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>160631</t>
+          <t>159375</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,26%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40157</t>
+          <t>39794</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62472</t>
+          <t>62688</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40092</t>
+          <t>39899</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61614</t>
+          <t>60769</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84008</t>
+          <t>83656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115840</t>
+          <t>115005</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>385418</t>
+          <t>385202</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407733</t>
+          <t>408096</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>426176</t>
+          <t>427021</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447698</t>
+          <t>447891</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>819840</t>
+          <t>820675</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>851672</t>
+          <t>852024</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>7189</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18086</t>
+          <t>18637</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23811</t>
+          <t>24583</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20523</t>
+          <t>21245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38450</t>
+          <t>38164</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>145232</t>
+          <t>144681</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>156578</t>
+          <t>156129</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146540</t>
+          <t>145768</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159130</t>
+          <t>159123</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>295220</t>
+          <t>295506</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>313147</t>
+          <t>312425</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61927</t>
+          <t>61693</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87534</t>
+          <t>87705</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68855</t>
+          <t>67687</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96516</t>
+          <t>95718</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134732</t>
+          <t>136554</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>173651</t>
+          <t>175619</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>616043</t>
+          <t>615872</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>641650</t>
+          <t>641884</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>647817</t>
+          <t>648615</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>675478</t>
+          <t>676646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1274259</t>
+          <t>1272291</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1313178</t>
+          <t>1311356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2016 (tasa de respuesta: 99,01%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2016 (tasa de respuesta: 99,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9807</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16009</t>
+          <t>16026</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49265</t>
+          <t>49007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56288</t>
+          <t>56294</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58882</t>
+          <t>58540</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66523</t>
+          <t>66461</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111420</t>
+          <t>111403</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121417</t>
+          <t>121659</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34667</t>
+          <t>34525</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55878</t>
+          <t>56119</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36848</t>
+          <t>36497</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58577</t>
+          <t>58516</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77038</t>
+          <t>77492</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108027</t>
+          <t>107147</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>411707</t>
+          <t>411466</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>432918</t>
+          <t>433060</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>425197</t>
+          <t>425258</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>446926</t>
+          <t>447277</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>843332</t>
+          <t>844212</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>874321</t>
+          <t>873867</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24022</t>
+          <t>23563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,47 +4640,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>16887</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11230</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>23994</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>9,07%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>6,03%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>16887</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10810</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>24014</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,07%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24985</t>
+          <t>25062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43246</t>
+          <t>43432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>146516</t>
+          <t>146975</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160260</t>
+          <t>159925</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,49 +4753,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>93,78%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>169270</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>162163</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>174927</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>90,93%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>87,11%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>93,97%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>169270</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>162143</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>175347</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,93%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>87,1%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>94,19%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>476</t>
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>313450</t>
+          <t>313264</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>331711</t>
+          <t>331634</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53124</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78190</t>
+          <t>78767</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56504</t>
+          <t>55483</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83849</t>
+          <t>82556</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>116934</t>
+          <t>117201</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>152569</t>
+          <t>152216</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>618748</t>
+          <t>618171</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>643814</t>
+          <t>643296</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>654697</t>
+          <t>655990</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>682042</t>
+          <t>683063</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1282914</t>
+          <t>1283267</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1318549</t>
+          <t>1318282</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8402</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14658</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19839</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46276</t>
+          <t>46300</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53065</t>
+          <t>53025</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47346</t>
+          <t>47221</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57647</t>
+          <t>57559</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96843</t>
+          <t>96516</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>108729</t>
+          <t>108977</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31930</t>
+          <t>32414</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54584</t>
+          <t>55298</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39990</t>
+          <t>40371</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65171</t>
+          <t>65409</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80212</t>
+          <t>78515</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113569</t>
+          <t>111874</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>403920</t>
+          <t>403206</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>426574</t>
+          <t>426090</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>451021</t>
+          <t>450783</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>476202</t>
+          <t>475821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>861128</t>
+          <t>862823</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>894485</t>
+          <t>896182</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18300</t>
+          <t>18347</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>15253</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30330</t>
+          <t>30420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26088</t>
+          <t>25765</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43955</t>
+          <t>45022</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>131251</t>
+          <t>131204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141934</t>
+          <t>141960</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153019</t>
+          <t>152929</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>168566</t>
+          <t>168096</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>288945</t>
+          <t>287878</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>306812</t>
+          <t>307135</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48026</t>
+          <t>47477</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73821</t>
+          <t>73561</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67496</t>
+          <t>67044</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98738</t>
+          <t>99187</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123293</t>
+          <t>121956</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>164986</t>
+          <t>164653</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>588912</t>
+          <t>589172</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>614707</t>
+          <t>615256</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>662807</t>
+          <t>662358</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>694049</t>
+          <t>694501</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1259292</t>
+          <t>1259625</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1300985</t>
+          <t>1302322</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP26C_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP26C_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,74 +723,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5796</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2666</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10804</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>12247</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7534</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18314</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7558</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18309</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>13,48%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>20,15%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5796</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3066</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11234</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,73%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>27</t>
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12134</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24955</t>
+          <t>25226</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>80345</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>75337</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>83475</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,27%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,46%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,91%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>78620</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>72553</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>83333</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>72558</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>83309</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>86,52%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>79,85%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>91,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>80345</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>74907</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>83075</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,27%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>86,96%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152053</t>
+          <t>151782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>164874</t>
+          <t>164777</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86141</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86141</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86141</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86141</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86141</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86141</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>46087</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36372</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>57302</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,12%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>47643</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>38472</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>58790</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>38659</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>59087</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>11,47%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14,15%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>46087</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>35975</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>57310</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77478</t>
+          <t>79401</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108334</t>
+          <t>110090</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>426796</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>415581</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>436511</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,25%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>556</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>367822</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>356675</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>376993</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>356378</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>376806</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,53%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>85,85%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>426796</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>415573</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>436908</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,25%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>780014</t>
+          <t>778258</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>810870</t>
+          <t>808947</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>472883</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>472883</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>472883</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>415465</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>415465</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>415465</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>472883</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>472883</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>472883</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,74 +1409,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15716</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10279</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22904</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>19017</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12978</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26452</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12964</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>26463</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>11,01%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>7,51%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>15,32%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15716</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10508</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22388</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>51</t>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26479</t>
+          <t>26451</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44834</t>
+          <t>44871</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>141089</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>133901</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>146526</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,98%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,39%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,44%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>153680</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>146245</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>159719</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>146234</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>159733</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>88,99%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>84,68%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>92,49%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>141089</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>134417</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>146297</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,98%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>85,72%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>93,3%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>435</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284668</t>
+          <t>284631</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>303023</t>
+          <t>303051</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>156805</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>156805</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>156805</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172697</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172697</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172697</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>156805</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>156805</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>156805</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>67600</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>56272</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>80488</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>78908</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>65682</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>92845</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>65895</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>93971</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,62%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>67600</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>55832</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>80371</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,44%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>129479</t>
+          <t>129378</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165012</t>
+          <t>166082</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>648228</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>635340</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>659556</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,14%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>898</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>600121</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>586184</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>613347</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>585058</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>613134</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>88,38%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86,33%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>974</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>648228</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>635457</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>659996</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,56%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1229846</t>
+          <t>1228776</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1265379</t>
+          <t>1265480</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1076</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>715828</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>715828</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>715828</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>679029</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>679029</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>679029</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1076</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>715828</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>715828</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>715828</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14506</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9592</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20556</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,83%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,13%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23,85%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10999</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6370</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16888</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6691</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17248</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>11,91%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14506</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9513</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>20988</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>16,83%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19186</t>
+          <t>18690</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34129</t>
+          <t>33662</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>71686</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>65636</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>76600</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,17%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>76,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,87%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>81370</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>75481</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>85999</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>75121</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>85678</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>88,09%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>81,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>71686</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>65204</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>76679</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>83,17%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144432</t>
+          <t>144899</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159375</t>
+          <t>159871</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>49577</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>39621</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>60839</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,16%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,12%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,47%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>50366</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>39794</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>62688</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>39594</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>61626</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>11,25%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,88%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>49577</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>39899</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>60769</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83656</t>
+          <t>85401</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115005</t>
+          <t>114392</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>438213</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>426951</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>448169</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,84%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,53%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>578</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>397524</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>385202</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>408096</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>386264</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>408296</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,75%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>438213</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>427021</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>447891</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>89,84%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>820675</t>
+          <t>821288</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>852024</t>
+          <t>850279</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,87%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>487790</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>487790</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>487790</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>447890</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>447890</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>447890</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>699</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>487790</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>487790</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>487790</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17200</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11784</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23944</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,1%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,06%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>11854</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7189</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18637</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6753</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>17844</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,26%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,41%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17200</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11228</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,1%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21245</t>
+          <t>22082</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38164</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>153151</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>146407</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158567</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,9%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,94%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>151464</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>144681</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>156129</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>145474</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>156565</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,74%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,59%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>153151</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>145768</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>159123</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,9%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>295506</t>
+          <t>295404</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>312425</t>
+          <t>311588</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>170351</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>170351</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>170351</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>163318</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>163318</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>163318</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>170351</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>170351</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>170351</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>81283</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>68247</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>96003</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,9%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>73218</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>61693</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>87705</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>60202</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>86826</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,41%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>81283</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>67687</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>95718</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,92%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136554</t>
+          <t>135745</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>175619</t>
+          <t>174869</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>663050</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>648330</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>676086</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,1%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,83%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>912</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>630359</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>615872</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>641884</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>616751</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>643375</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>89,59%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>663050</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>648615</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>676646</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>89,08%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1272291</t>
+          <t>1273041</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1311356</t>
+          <t>1312165</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744333</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744333</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744333</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1014</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>703577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>703577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>703577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744333</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744333</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744333</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5060</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2144</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9744</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5100</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2520</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9807</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2361</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9248</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,67%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,67%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5060</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2153</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10074</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16026</t>
+          <t>16112</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>63554</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>58870</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>66470</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,63%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,8%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>53714</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49007</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>56294</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>49566</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>56453</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,33%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>83,33%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>63554</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>58540</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>66461</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,63%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111403</t>
+          <t>111317</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121659</t>
+          <t>121685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>58814</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>58814</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>58814</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>46705</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>37217</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>58891</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>44280</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>34525</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>56119</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>34526</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>54973</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,47%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>7,38%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>46705</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>36497</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>58516</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,65%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77492</t>
+          <t>77576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107147</t>
+          <t>107274</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -4385,74 +4385,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>437069</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>424883</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>446557</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>641</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>423305</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>411466</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>433060</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>412612</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>433059</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,53%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>88,24%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>92,62%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>437069</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>425258</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>447277</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,35%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>87,9%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>92,46%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1263</t>
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>844212</t>
+          <t>844085</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>873867</t>
+          <t>873783</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>483774</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>483774</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>483774</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>706</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>467585</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>467585</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>467585</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>483774</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>483774</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>483774</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4620,67 +4620,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>16887</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11597</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>24030</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,07%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,91%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>16160</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10613</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23563</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10378</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>23296</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,48%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>16887</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11230</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>23994</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,07%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25062</t>
+          <t>24828</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43432</t>
+          <t>43037</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>169270</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>162127</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>174560</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,93%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,09%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,77%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154378</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>146975</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>159925</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>147242</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>160160</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>90,52%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,78%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>169270</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>162163</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>174927</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,93%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>313264</t>
+          <t>313659</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>331634</t>
+          <t>331868</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>186157</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>186157</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>186157</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>170538</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>170538</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>170538</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>186157</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>186157</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>186157</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4963,67 +4963,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>68652</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>56425</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>82320</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>65539</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>53642</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>78767</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>52926</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>78613</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,4%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>68652</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>55483</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>82556</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117201</t>
+          <t>117083</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>152216</t>
+          <t>153372</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>669894</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>656226</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>682121</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,7%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,85%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,36%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>952</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>631399</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>618171</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>643296</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>618325</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>644012</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>90,6%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>669894</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>655990</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>683063</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,7%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1283267</t>
+          <t>1282111</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1318282</t>
+          <t>1318400</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1056</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>738546</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>738546</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>738546</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1049</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>696938</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>696938</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>696938</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1056</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>738546</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>738546</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>738546</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8879</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4770</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14486</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8,41%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>25,53%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4131</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1653</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8378</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12918</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>8118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20166</t>
+          <t>20185</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47853</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>42246</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>51962</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>84,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>74,47%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>91,59%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>50547</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>46300</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>53025</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>92,44%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,68%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53217</t>
+          <t>42422</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47221</t>
+          <t>38501</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57559</t>
+          <t>44994</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>103764</t>
+          <t>90275</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96516</t>
+          <t>83305</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>108977</t>
+          <t>95372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>49869</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>39088</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>63105</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,28%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>43204</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>32414</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>55298</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,06%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52384</t>
+          <t>43496</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40371</t>
+          <t>33861</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65409</t>
+          <t>54866</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>95589</t>
+          <t>93365</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78515</t>
+          <t>77272</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111874</t>
+          <t>109768</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>425452</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>412216</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>436233</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,72%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>575</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>415300</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>403206</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>426090</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>90,58%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,93%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>463808</t>
+          <t>386890</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>450783</t>
+          <t>375520</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>475821</t>
+          <t>396525</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>879108</t>
+          <t>812342</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>862823</t>
+          <t>795939</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>896182</t>
+          <t>828435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475321</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475321</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475321</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>641</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>458504</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>458504</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>458504</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516192</t>
+          <t>430386</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516192</t>
+          <t>430386</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516192</t>
+          <t>430386</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>974697</t>
+          <t>905707</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>974697</t>
+          <t>905707</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>974697</t>
+          <t>905707</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20368</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13426</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28317</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,81%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12384</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7591</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18347</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21625</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30420</t>
+          <t>19271</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>34009</t>
+          <t>33312</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>24676</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45022</t>
+          <t>42644</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>148051</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>140102</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>154993</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,91%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>83,19%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,03%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>137167</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>131204</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>141960</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>91,72%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,92%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>161724</t>
+          <t>137032</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152929</t>
+          <t>130705</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>168096</t>
+          <t>141624</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>298891</t>
+          <t>285083</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>287878</t>
+          <t>275751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>307135</t>
+          <t>293719</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>79116</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>63956</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>94496</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,13%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13,49%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>59719</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>47477</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>73561</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9,01%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>82796</t>
+          <t>60776</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67044</t>
+          <t>48759</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99187</t>
+          <t>73877</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>142515</t>
+          <t>139892</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>121956</t>
+          <t>122446</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>164653</t>
+          <t>160807</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>621356</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>605976</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>636516</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>86,51%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,87%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>845</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>603014</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>589172</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>615256</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>90,99%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,9%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,84%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>678749</t>
+          <t>566344</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>662358</t>
+          <t>553243</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>694501</t>
+          <t>578361</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1281763</t>
+          <t>1187700</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1259625</t>
+          <t>1166785</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1302322</t>
+          <t>1205146</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>90,78%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700472</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700472</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700472</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>940</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>662733</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>662733</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>662733</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761545</t>
+          <t>627120</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761545</t>
+          <t>627120</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761545</t>
+          <t>627120</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1424278</t>
+          <t>1327592</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1424278</t>
+          <t>1327592</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1424278</t>
+          <t>1327592</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
